--- a/employee_surveys/042_employee_communication_survey--employee_surveys.xlsx
+++ b/employee_surveys/042_employee_communication_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How often do you think you should be communicating with team members?</t>
+          <t>Communication Style Frequency</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Do you have any comments or suggestions on how to improve communication in your team?</t>
+          <t>Employee Communication Survey Comments</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What questions would you like to see on the employee communication survey?</t>
+          <t>Employee Communication Survey Questions</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Do you have any comments or suggestions on how to improve communication in your team?</t>
+          <t>Communication Survey Comments</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What questions would you like to see on the employee communication survey?</t>
+          <t>Communication Survey Questions 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Do you have any suggestions on how to improve communication in your team?</t>
+          <t>Communication Survey Suggestions</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>How often do you think you should be having team dynamics?</t>
+          <t>Effective Communication</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1874,17 +1874,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>communication_effectiveness_choices</t>
+          <t>communication_challenges_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>language_barrier</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Language barrier</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>language_barrier</t>
+          <t>cultural_difference</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Language barrier</t>
+          <t>Cultural difference</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>cultural_difference</t>
+          <t>time_zone_difference</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cultural difference</t>
+          <t>Time zone difference</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>time_zone_difference</t>
+          <t>lack_of_feedback</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Time zone difference</t>
+          <t>Lack of feedback</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>lack_of_feedback</t>
+          <t>lack_of_trust</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lack of feedback</t>
+          <t>Lack of trust</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>lack_of_trust</t>
+          <t>poor_internet_connectivity</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lack of trust</t>
+          <t>Poor internet connectivity</t>
         </is>
       </c>
     </row>
@@ -1981,29 +1981,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>poor_internet_connectivity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poor internet connectivity</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>communication_challenges_choices</t>
+          <t>communication_satisfaction_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Very dissatisfied</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Somewhat dissatisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -2066,29 +2066,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Somewhat satisfied</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>communication_satisfaction_choices</t>
+          <t>team_dynamics_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>team_members_know_and_appreciate_each_other</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Very satisfied</t>
+          <t>Team members know and appreciate each other</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>team_members_know_and_appreciate_each_other</t>
+          <t>team_members_are_willing_to_share_their_thoughts_and_ideas</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Team members know and appreciate each other</t>
+          <t>Team members are willing to share their thoughts and ideas</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>team_members_are_willing_to_share_their_thoughts_and_ideas</t>
+          <t>team_members_are_open-minded_and_adaptable</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Team members are willing to share their thoughts and ideas</t>
+          <t>Team members are open-minded and adaptable</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>team_members_are_open-minded_and_adaptable</t>
+          <t>team_members_are_collaborative_and_supportive</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Team members are open-minded and adaptable</t>
+          <t>Team members are collaborative and supportive</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>team_members_are_collaborative_and_supportive</t>
+          <t>team_members_are_motivated_and_engaged</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Team members are collaborative and supportive</t>
+          <t>Team members are motivated and engaged</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>team_members_are_motivated_and_engaged</t>
+          <t>team_members_are_respectful_and_considerate</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Team members are motivated and engaged</t>
+          <t>Team members are respectful and considerate</t>
         </is>
       </c>
     </row>
@@ -2185,29 +2185,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>team_members_are_respectful_and_considerate</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Team members are respectful and considerate</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>team_dynamics_choices</t>
+          <t>team_dynamics_frequency_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>less_than_weekly</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Less than weekly</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>less_than_weekly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Less than weekly</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -2287,29 +2287,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>team_dynamics_frequency_choices</t>
+          <t>effective_communication_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>less_than_weekly</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Less than weekly</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>less_than_weekly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Less than weekly</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -2389,29 +2389,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>effective_communication_choices</t>
+          <t>team_dynamics_satisfaction_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Very dissatisfied</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Somewhat dissatisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -2474,27 +2474,10 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
-        <is>
-          <t>Somewhat satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>team_dynamics_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
         <is>
           <t>Very satisfied</t>
         </is>
